--- a/Assets/Project/Csv/Item/3. Material.xlsx
+++ b/Assets/Project/Csv/Item/3. Material.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\GitLab\Dairy Farm\Assets\Project\Csv\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFDC3F5-30F1-40FD-B4E7-0795CDD74818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5983A39-95F3-4A96-A682-660378D1F2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1455" yWindow="2775" windowWidth="21600" windowHeight="11295" xr2:uid="{F5EC58A1-2CB0-4597-AD94-4C4B1A7FFC79}"/>
+    <workbookView xWindow="1800" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{F5EC58A1-2CB0-4597-AD94-4C4B1A7FFC79}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,10 +58,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>쌀 1가마</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>수확한 쌀을 쌀가마니에 모았다</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -87,6 +83,10 @@
   </si>
   <si>
     <t>속이 꽉찬 호박이다. 할로윈에 쓸만해 보인다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쌀 200g</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -570,10 +570,10 @@
         <v>10001</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="D2" s="2">
         <v>99</v>
@@ -587,10 +587,10 @@
         <v>10101</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>8</v>
       </c>
       <c r="D3" s="5">
         <v>99</v>
@@ -604,10 +604,10 @@
         <v>10201</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2">
         <v>99</v>
@@ -621,10 +621,10 @@
         <v>10301</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>10</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="D5" s="5">
         <v>99</v>
